--- a/llm-classifier/results/llm_distribution_llama3.1_8b.xlsx
+++ b/llm-classifier/results/llm_distribution_llama3.1_8b.xlsx
@@ -440,10 +440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C4" t="n">
-        <v>31.8</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="9">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>10.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="14">
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -612,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16">
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="18">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19">
@@ -664,7 +664,7 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>2.8</v>
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="23">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="24">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="C25" t="n">
         <v>100</v>
